--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N156_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N156_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.52035679605831</v>
+        <v>2.197057979359474</v>
       </c>
       <c r="D2" t="n">
-        <v>5.852349955359813</v>
+        <v>0.9510068677459697</v>
       </c>
       <c r="E2" t="n">
-        <v>10.42725231201724</v>
+        <v>1.694428500702802</v>
       </c>
       <c r="F2" t="n">
-        <v>11.619826622889</v>
+        <v>1.888221826219463</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.0981341698694</v>
+        <v>2.128446802603777</v>
       </c>
       <c r="D3" t="n">
-        <v>13.64748844264038</v>
+        <v>2.217716871929061</v>
       </c>
       <c r="E3" t="n">
-        <v>10.42725231201724</v>
+        <v>1.694428500702802</v>
       </c>
       <c r="F3" t="n">
-        <v>11.619826622889</v>
+        <v>1.888221826219463</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.1925241636632</v>
+        <v>3.118785176595271</v>
       </c>
       <c r="D4" t="n">
-        <v>19.76616766368038</v>
+        <v>3.212002245348062</v>
       </c>
       <c r="E4" t="n">
-        <v>10.42725231201724</v>
+        <v>1.694428500702802</v>
       </c>
       <c r="F4" t="n">
-        <v>11.619826622889</v>
+        <v>1.888221826219463</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.36899237133863</v>
+        <v>5.584961260342529</v>
       </c>
       <c r="D5" t="n">
-        <v>34.65355018547302</v>
+        <v>5.631201905139366</v>
       </c>
       <c r="E5" t="n">
-        <v>10.42725231201724</v>
+        <v>1.694428500702802</v>
       </c>
       <c r="F5" t="n">
-        <v>11.619826622889</v>
+        <v>1.888221826219463</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.34550080644673</v>
+        <v>5.906143881047594</v>
       </c>
       <c r="D6" t="n">
-        <v>35.43811250977239</v>
+        <v>5.758693282838014</v>
       </c>
       <c r="E6" t="n">
-        <v>10.42725231201724</v>
+        <v>1.694428500702802</v>
       </c>
       <c r="F6" t="n">
-        <v>11.619826622889</v>
+        <v>1.888221826219463</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.53324308565454</v>
+        <v>6.099152001418863</v>
       </c>
       <c r="D7" t="n">
-        <v>36.33998788048427</v>
+        <v>5.905248030578695</v>
       </c>
       <c r="E7" t="n">
-        <v>10.42725231201724</v>
+        <v>1.694428500702802</v>
       </c>
       <c r="F7" t="n">
-        <v>11.619826622889</v>
+        <v>1.888221826219463</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.52246544480766</v>
+        <v>5.772400634781246</v>
       </c>
       <c r="D8" t="n">
-        <v>34.78750015760252</v>
+        <v>5.65296877561041</v>
       </c>
       <c r="E8" t="n">
-        <v>10.42725231201724</v>
+        <v>1.694428500702802</v>
       </c>
       <c r="F8" t="n">
-        <v>11.619826622889</v>
+        <v>1.888221826219463</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
